--- a/docs/ホテル個別設定ヒアリングシート.xlsx
+++ b/docs/ホテル個別設定ヒアリングシート.xlsx
@@ -13,7 +13,7 @@
     <sheet name="全体意見" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ヒアリング項目'!$A$1:$K$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ヒアリング項目'!$A$1:$K$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C30"/>
+  <dimension ref="B2:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>v1.0（2026-09）｜ 設問 94 項目</t>
+          <t>v1.1（2026-09）｜ 設問 110 項目</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>「高」は初期設定に必須の項目です。お時間が取れない場合は「高」（45問）だけでも埋めてください。</t>
+          <t>「高」は初期設定に必須の項目です。お時間が取れない場合は「高」（51問）だけでも埋めてください。</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>全94問で40〜60分。「高」のみなら20〜30分です。</t>
+          <t>全110問で45〜70分。「高」のみなら25〜35分です。</t>
         </is>
       </c>
     </row>
@@ -699,86 +699,86 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>12 問（うち重要度「高」 4 問）</t>
+          <t>13 問（うち重要度「高」 5 問）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>カレンダー</t>
+          <t>予算・目標</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>5 問（うち重要度「高」 3 問）</t>
+          <t>5 問（うち重要度「高」 2 問）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>料金ランク</t>
+          <t>カレンダー</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>8 問（うち重要度「高」 4 問）</t>
+          <t>7 問（うち重要度「高」 4 問）</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>価格運用</t>
+          <t>料金ランク</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>14 問（うち重要度「高」 6 問）</t>
+          <t>9 問（うち重要度「高」 5 問）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>10 問（うち重要度「高」 2 問）</t>
+          <t>16 問（うち重要度「高」 6 問）</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>15 問（うち重要度「高」 11 問）</t>
+          <t>10 問（うち重要度「高」 2 問）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>セグメント・団体</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>8 問（うち重要度「高」 3 問）</t>
+          <t>15 問（うち重要度「高」 11 問）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>競合・チャネル</t>
+          <t>セグメント・団体</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -790,12 +790,24 @@
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
+          <t>競合・チャネル</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>9 問（うち重要度「高」 4 問）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
           <t>運用体制</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>6 問（うち重要度「高」 2 問）</t>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>10 問（うち重要度「高」 2 問）</t>
         </is>
       </c>
     </row>
@@ -810,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1873,86 +1885,86 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>■ カレンダー</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="9" t="n"/>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>K-01</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>カレンダー</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>現在「週末」として扱っている曜日</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>M-13</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>指標定義</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>宿泊税・入湯税等の扱い（料金に含むか、別建てか）</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>選択</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>金土,土日,金土日,その他</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>金土</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>料金に含む,別建て,課税なし</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>別建て</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="12" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr">
-        <is>
-          <t>A-22</t>
-        </is>
-      </c>
-      <c r="K25" s="11" t="inlineStr">
-        <is>
-          <t>Hotel.weekendDays</t>
-        </is>
-      </c>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>§2.2</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>■ 予算・目標</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="9" t="n"/>
+      <c r="I25" s="9" t="n"/>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="9" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>K-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>カレンダー</t>
+          <t>予算・目標</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>「週末」ではなく「休前日（翌日が休み）」で管理したいか</t>
+          <t>月次予算（売上・販売室数・ADR・稼働率・宿泊人数）をご提供いただけますか</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
@@ -1962,12 +1974,12 @@
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>休前日で管理したい,曜日固定でよい</t>
+          <t>提供できる,一部のみ,提供できない</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>休前日で管理したい</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="6" t="n"/>
@@ -1979,37 +1991,41 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>A-22 / AG-03</t>
+          <t>§3.2</t>
         </is>
       </c>
       <c r="K26" s="11" t="inlineStr">
         <is>
-          <t>AG-03</t>
+          <t>MonthlyBudget</t>
         </is>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>K-03</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>カレンダー</t>
+          <t>予算・目標</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>施設固有の繁忙要因（近隣イベント・学会・受験期など）</t>
+          <t>前年実績を月次でご提供いただけますか</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>提供できる,一部のみ,提供できない</t>
+        </is>
+      </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -2024,44 +2040,44 @@
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>C-21</t>
+          <t>§3.2</t>
         </is>
       </c>
       <c r="K27" s="11" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>MonthlyBudget</t>
         </is>
       </c>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>K-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>カレンダー</t>
+          <t>予算・目標</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>需要に効く季節要因（該当するものすべて）</t>
+          <t>予算の管理単位</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
+          <t>選択</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>春節 / 桜 / GW / 夏休み / 紅葉 / 年末年始 / 台風 / その他</t>
+          <t>施設全体のみ,客室タイプ別,セグメント別,併用</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>施設全体のみ</t>
         </is>
       </c>
       <c r="G28" s="6" t="n"/>
@@ -2073,136 +2089,144 @@
       </c>
       <c r="J28" s="11" t="inlineStr">
         <is>
-          <t>C-21</t>
+          <t>§3.2</t>
         </is>
       </c>
       <c r="K28" s="11" t="inlineStr">
         <is>
-          <t>DailyData.externalFactors</t>
+          <t>MonthlyBudget</t>
         </is>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>K-05</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>カレンダー</t>
+          <t>予算・目標</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>天候が需要に影響する日数（何日前から効くか）</t>
+          <t>日別の予算（日割り）をお持ちですか</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>数値</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>持っている,持っていない</t>
+        </is>
+      </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>7日</t>
+          <t>持っていない</t>
         </is>
       </c>
       <c r="G29" s="6" t="n"/>
       <c r="H29" s="6" t="n"/>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>C-22</t>
+          <t>§3.2</t>
         </is>
       </c>
       <c r="K29" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>■ 料金ランク</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="9" t="n"/>
-      <c r="I30" s="9" t="n"/>
-      <c r="J30" s="9" t="n"/>
-      <c r="K30" s="9" t="n"/>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>料金ランク</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>現在運用している料金ランクの段階数</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>数値</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr"/>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="n"/>
-      <c r="I31" s="12" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="J31" s="11" t="inlineStr">
-        <is>
-          <t>E-05 / AG-02</t>
-        </is>
-      </c>
-      <c r="K31" s="11" t="inlineStr">
-        <is>
-          <t>PriceRank</t>
-        </is>
-      </c>
+          <t>MonthlyBudget</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>B-05</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>予算・目標</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>予算に対して最も重視される指標</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>売上,稼働率,ADR,RevPAR</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>売上</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>§3.2</t>
+        </is>
+      </c>
+      <c r="K30" s="11" t="inlineStr">
+        <is>
+          <t>F-DASH-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>■ カレンダー</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="9" t="n"/>
+      <c r="I31" s="9" t="n"/>
+      <c r="J31" s="9" t="n"/>
+      <c r="K31" s="9" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>K-01</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>料金ランク</t>
+          <t>カレンダー</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>ランクの刻み幅</t>
+          <t>現在「週末」として扱っている曜日</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
@@ -2212,12 +2236,12 @@
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>等比（%）,実額（円）,不定</t>
+          <t>金土,土日,金土日,その他</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>等比3〜5%/段</t>
+          <t>金土</t>
         </is>
       </c>
       <c r="G32" s="6" t="n"/>
@@ -2229,40 +2253,44 @@
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>A-22</t>
         </is>
       </c>
       <c r="K32" s="11" t="inlineStr">
         <is>
-          <t>PriceRank</t>
+          <t>Hotel.weekendDays</t>
         </is>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>K-02</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>料金ランク</t>
+          <t>カレンダー</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>（等比の場合）1段あたりの%／（実額の場合）1段あたりの円</t>
+          <t>「週末」ではなく「休前日（翌日が休み）」で管理したいか</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>休前日で管理したい,曜日固定でよい</t>
+        </is>
+      </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>休前日で管理したい</t>
         </is>
       </c>
       <c r="G33" s="6" t="n"/>
@@ -2274,93 +2302,89 @@
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>A-22 / AG-03</t>
         </is>
       </c>
       <c r="K33" s="11" t="inlineStr">
         <is>
-          <t>PriceRank</t>
+          <t>AG-03</t>
         </is>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>K-03</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>料金ランク</t>
+          <t>カレンダー</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>中央ランク（標準価格）の考え方</t>
+          <t>施設固有の繁忙要因（近隣イベント・学会・受験期など）</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>固定,月別に変える,設定なし</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr"/>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>固定</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="6" t="n"/>
       <c r="H34" s="6" t="n"/>
-      <c r="I34" s="11" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>C-21</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr">
         <is>
-          <t>PriceRank</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>K-04</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>料金ランク</t>
+          <t>カレンダー</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>ランク表示の基準人数</t>
+          <t>需要に効く季節要因（該当するものすべて）</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
+          <t>自由記述</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>1名基準,2名基準</t>
+          <t>春節 / 桜 / GW / 夏休み / 紅葉 / 年末年始 / 台風 / その他</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>2名基準</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="6" t="n"/>
@@ -2372,89 +2396,85 @@
       </c>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>F-07</t>
+          <t>C-21</t>
         </is>
       </c>
       <c r="K35" s="11" t="inlineStr">
         <is>
-          <t>F-SET-02</t>
+          <t>DailyData.externalFactors</t>
         </is>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>K-05</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>料金ランク</t>
+          <t>カレンダー</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>人数別価格の倍率（1名を1.0とした2名/3名/4名）</t>
+          <t>天候が需要に影響する日数（何日前から効くか）</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
+          <t>数値</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr"/>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>1.7 / 1.35 / 1.2</t>
+          <t>7日</t>
         </is>
       </c>
       <c r="G36" s="6" t="n"/>
       <c r="H36" s="6" t="n"/>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="J36" s="11" t="inlineStr">
         <is>
-          <t>F-08</t>
+          <t>C-22</t>
         </is>
       </c>
       <c r="K36" s="11" t="inlineStr">
         <is>
-          <t>PriceRank</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>K-06</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>料金ランク</t>
+          <t>カレンダー</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>部屋タイプ間の価格の持ち方</t>
+          <t>繁忙期・閑散期にあたる月をお聞かせください</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>標準タイプからの差額,タイプ別に独立したランク</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr"/>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>差額方式</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="6" t="n"/>
@@ -2466,29 +2486,29 @@
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>F-11 / E-25</t>
+          <t>§3.2</t>
         </is>
       </c>
       <c r="K37" s="11" t="inlineStr">
         <is>
-          <t>DailyRoomData</t>
+          <t>GroupBooking / F-DP-01</t>
         </is>
       </c>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>K-07</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>料金ランク</t>
+          <t>カレンダー</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>実務上の上限ランク・下限ランク</t>
+          <t>休館日・大規模メンテナンスのご予定</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
@@ -2499,7 +2519,7 @@
       <c r="E38" s="11" t="inlineStr"/>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>下限R05 / 上限R38</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G38" s="6" t="n"/>
@@ -2511,19 +2531,19 @@
       </c>
       <c r="J38" s="11" t="inlineStr">
         <is>
-          <t>E-09</t>
+          <t>§2</t>
         </is>
       </c>
       <c r="K38" s="11" t="inlineStr">
         <is>
-          <t>PriceRank.isActive</t>
+          <t>DailyData</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>■ 価格運用</t>
+          <t>■ 料金ランク</t>
         </is>
       </c>
       <c r="B39" s="9" t="n"/>
@@ -2540,32 +2560,28 @@
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>V-01</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>価格運用</t>
+          <t>料金ランク</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>価格決定の基本方針（最重要）</t>
+          <t>現在運用している料金ランクの段階数</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>売上最大化,単価優先（稼働を落としても高単価）,前日より値下げしない,その他</t>
-        </is>
-      </c>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr"/>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>売上最大化</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G40" s="6" t="n"/>
@@ -2577,40 +2593,44 @@
       </c>
       <c r="J40" s="11" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>E-05 / AG-02</t>
         </is>
       </c>
       <c r="K40" s="11" t="inlineStr">
         <is>
-          <t>PricingStrategyConfig</t>
+          <t>PriceRank</t>
         </is>
       </c>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>V-02</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>価格運用</t>
+          <t>料金ランク</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>（その他・補足）方針の具体的な内容</t>
+          <t>ランクの刻み幅</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E41" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>等比（%）,実額（円）,不定</t>
+        </is>
+      </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>等比3〜5%/段</t>
         </is>
       </c>
       <c r="G41" s="6" t="n"/>
@@ -2622,40 +2642,40 @@
       </c>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="K41" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PriceRank</t>
         </is>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>V-03</t>
+          <t>R-03</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>価格運用</t>
+          <t>料金ランク</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>戦略の重み 稼働率（%）</t>
+          <t>（等比の場合）1段あたりの%／（実額の場合）1段あたりの円</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>数値</t>
+          <t>自由記述</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr"/>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="6" t="n"/>
@@ -2667,130 +2687,138 @@
       </c>
       <c r="J42" s="11" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="K42" s="11" t="inlineStr">
         <is>
-          <t>PricingStrategyConfig.weightOccupancy</t>
+          <t>PriceRank</t>
         </is>
       </c>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>V-04</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>価格運用</t>
+          <t>料金ランク</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>戦略の重み ADR（%）</t>
+          <t>中央ランク（標準価格）の考え方</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>数値</t>
-        </is>
-      </c>
-      <c r="E43" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>固定,月別に変える,設定なし</t>
+        </is>
+      </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>固定</t>
         </is>
       </c>
       <c r="G43" s="6" t="n"/>
       <c r="H43" s="6" t="n"/>
-      <c r="I43" s="12" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="K43" s="11" t="inlineStr">
         <is>
-          <t>PricingStrategyConfig.weightAdr</t>
+          <t>PriceRank</t>
         </is>
       </c>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>V-05</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>価格運用</t>
+          <t>料金ランク</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>戦略の重み 競合追従（%）※合計100</t>
+          <t>ランク表示の基準人数</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>数値</t>
-        </is>
-      </c>
-      <c r="E44" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>1名基準,2名基準</t>
+        </is>
+      </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2名基準</t>
         </is>
       </c>
       <c r="G44" s="6" t="n"/>
       <c r="H44" s="6" t="n"/>
-      <c r="I44" s="12" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="J44" s="11" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>F-07</t>
         </is>
       </c>
       <c r="K44" s="11" t="inlineStr">
         <is>
-          <t>PricingStrategyConfig.weightCompetitor</t>
+          <t>F-SET-02</t>
         </is>
       </c>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>V-06</t>
+          <t>R-06</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>価格運用</t>
+          <t>料金ランク</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>1日あたりの価格変更幅の上限（ランク数）</t>
+          <t>人数別価格の倍率（1名を1.0とした2名/3名/4名）</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>数値</t>
+          <t>自由記述</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr"/>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.7 / 1.35 / 1.2</t>
         </is>
       </c>
       <c r="G45" s="6" t="n"/>
@@ -2802,29 +2830,29 @@
       </c>
       <c r="J45" s="11" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>F-08</t>
         </is>
       </c>
       <c r="K45" s="11" t="inlineStr">
         <is>
-          <t>F-DP-01</t>
+          <t>PriceRank</t>
         </is>
       </c>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>V-07</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>価格運用</t>
+          <t>料金ランク</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>値上げと値下げで変更幅を変えるか</t>
+          <t>部屋タイプ間の価格の持ち方</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
@@ -2834,61 +2862,57 @@
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>変える,同じ</t>
+          <t>標準タイプからの差額,タイプ別に独立したランク</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
-          <t>変える（上げ+2 / 下げ−1）</t>
+          <t>差額方式</t>
         </is>
       </c>
       <c r="G46" s="6" t="n"/>
       <c r="H46" s="6" t="n"/>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="J46" s="11" t="inlineStr">
         <is>
-          <t>E-14</t>
+          <t>F-11 / E-25</t>
         </is>
       </c>
       <c r="K46" s="11" t="inlineStr">
         <is>
-          <t>F-DP-01</t>
+          <t>DailyRoomData</t>
         </is>
       </c>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>V-08</t>
+          <t>R-08</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>価格運用</t>
+          <t>料金ランク</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>最小の変更単位</t>
+          <t>実務上の上限ランク・下限ランク</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E47" s="11" t="inlineStr">
-        <is>
-          <t>1ランク,2ランク以上</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr"/>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>1ランク</t>
+          <t>下限R05 / 上限R38</t>
         </is>
       </c>
       <c r="G47" s="6" t="n"/>
@@ -2900,29 +2924,29 @@
       </c>
       <c r="J47" s="11" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>E-09</t>
         </is>
       </c>
       <c r="K47" s="11" t="inlineStr">
         <is>
-          <t>F-DP-01</t>
+          <t>PriceRank.isActive</t>
         </is>
       </c>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>V-09</t>
+          <t>R-09</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>価格運用</t>
+          <t>料金ランク</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>価格変更の頻度上限</t>
+          <t>現行の料金ランク表（各ランクの実額）をご提供いただけますか</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
@@ -2932,81 +2956,53 @@
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>1日1回,1日2回,制限なし</t>
+          <t>提供できる,提供できない,作成中</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>1日1回（直前7日は2回）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G48" s="6" t="n"/>
       <c r="H48" s="6" t="n"/>
-      <c r="I48" s="11" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr">
         <is>
-          <t>E-31</t>
+          <t>§3.2</t>
         </is>
       </c>
       <c r="K48" s="11" t="inlineStr">
         <is>
-          <t>F-DP-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>V-10</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>価格運用</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>繁忙日に段階的値上げを始める稼働率の節目</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
-        <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E49" s="11" t="inlineStr"/>
-      <c r="F49" s="11" t="inlineStr">
-        <is>
-          <t>50 / 70 / 85%</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="n"/>
-      <c r="H49" s="6" t="n"/>
-      <c r="I49" s="11" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="J49" s="11" t="inlineStr">
-        <is>
-          <t>E-16</t>
-        </is>
-      </c>
-      <c r="K49" s="11" t="inlineStr">
-        <is>
-          <t>F-DP-01</t>
-        </is>
-      </c>
+          <t>PriceRank</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>■ 価格運用</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="9" t="n"/>
+      <c r="I49" s="9" t="n"/>
+      <c r="J49" s="9" t="n"/>
+      <c r="K49" s="9" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>V-11</t>
+          <t>V-01</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
@@ -3016,7 +3012,7 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>残室が僅少（5%以下）のとき価格を上限で維持するか</t>
+          <t>価格決定の基本方針（最重要）</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
@@ -3026,36 +3022,36 @@
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>維持する,通常どおり</t>
+          <t>売上最大化,単価優先（稼働を落としても高単価）,前日より値下げしない,その他</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>維持する</t>
+          <t>売上最大化</t>
         </is>
       </c>
       <c r="G50" s="6" t="n"/>
       <c r="H50" s="6" t="n"/>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="J50" s="11" t="inlineStr">
         <is>
-          <t>E-17</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="K50" s="11" t="inlineStr">
         <is>
-          <t>F-DP-01</t>
+          <t>PricingStrategyConfig</t>
         </is>
       </c>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>V-12</t>
+          <t>V-02</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -3065,22 +3061,18 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>直前（3日前以内）の値下げを認めるか</t>
+          <t>（その他・補足）方針の具体的な内容</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E51" s="11" t="inlineStr">
-        <is>
-          <t>条件付きで認める,認めない,制限なし</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr"/>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>条件付き</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G51" s="6" t="n"/>
@@ -3092,19 +3084,19 @@
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>E-19 / R-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>V-13</t>
+          <t>V-03</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
@@ -3114,46 +3106,42 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>価格の下限を原価から算出しているか</t>
+          <t>戦略の重み 稼働率（%）</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E52" s="11" t="inlineStr">
-        <is>
-          <t>算出している,していない</t>
-        </is>
-      </c>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr"/>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>していない</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G52" s="6" t="n"/>
       <c r="H52" s="6" t="n"/>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="I52" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="J52" s="11" t="inlineStr">
         <is>
-          <t>E-34</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="K52" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PricingStrategyConfig.weightOccupancy</t>
         </is>
       </c>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>V-14</t>
+          <t>V-04</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
@@ -3163,88 +3151,108 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>返金不可プラン・早割プランの有無</t>
+          <t>戦略の重み ADR（%）</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E53" s="11" t="inlineStr">
-        <is>
-          <t>両方あり,早割のみ,返金不可のみ,なし</t>
-        </is>
-      </c>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr"/>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G53" s="6" t="n"/>
       <c r="H53" s="6" t="n"/>
-      <c r="I53" s="11" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="I53" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>E-26</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="K53" s="11" t="inlineStr">
         <is>
-          <t>Campaign</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>■ 在庫・販売制限</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="n"/>
-      <c r="C54" s="9" t="n"/>
-      <c r="D54" s="9" t="n"/>
-      <c r="E54" s="9" t="n"/>
-      <c r="F54" s="9" t="n"/>
-      <c r="G54" s="9" t="n"/>
-      <c r="H54" s="9" t="n"/>
-      <c r="I54" s="9" t="n"/>
-      <c r="J54" s="9" t="n"/>
-      <c r="K54" s="9" t="n"/>
+          <t>PricingStrategyConfig.weightAdr</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>V-05</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>価格運用</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>戦略の重み 競合追従（%）※合計100</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr"/>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="n"/>
+      <c r="H54" s="6" t="n"/>
+      <c r="I54" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr">
+        <is>
+          <t>E-02</t>
+        </is>
+      </c>
+      <c r="K54" s="11" t="inlineStr">
+        <is>
+          <t>PricingStrategyConfig.weightCompetitor</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>S-01</t>
+          <t>V-06</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>CTA（到着日クローズ）を使うか</t>
+          <t>1日あたりの価格変更幅の上限（ランク数）</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E55" s="11" t="inlineStr">
-        <is>
-          <t>使う,使わない</t>
-        </is>
-      </c>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr"/>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>使わない</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G55" s="6" t="n"/>
@@ -3256,29 +3264,29 @@
       </c>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="K55" s="11" t="inlineStr">
         <is>
-          <t>推奨提示のみ</t>
+          <t>F-DP-01</t>
         </is>
       </c>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>S-02</t>
+          <t>V-07</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>CTD（出発日クローズ）を使うか</t>
+          <t>値上げと値下げで変更幅を変えるか</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
@@ -3288,46 +3296,46 @@
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>使う,使わない</t>
+          <t>変える,同じ</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
-          <t>使わない</t>
+          <t>変える（上げ+2 / 下げ−1）</t>
         </is>
       </c>
       <c r="G56" s="6" t="n"/>
       <c r="H56" s="6" t="n"/>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="J56" s="11" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="K56" s="11" t="inlineStr">
         <is>
-          <t>推奨提示のみ</t>
+          <t>F-DP-01</t>
         </is>
       </c>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>S-03</t>
+          <t>V-08</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>繁忙時に高手数料チャネルを売り止めるか</t>
+          <t>最小の変更単位</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
@@ -3337,12 +3345,12 @@
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>売り止める,売り止めない</t>
+          <t>1ランク,2ランク以上</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>売り止める</t>
+          <t>1ランク</t>
         </is>
       </c>
       <c r="G57" s="6" t="n"/>
@@ -3354,134 +3362,138 @@
       </c>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="K57" s="11" t="inlineStr">
         <is>
-          <t>OtaChannelData</t>
+          <t>F-DP-01</t>
         </is>
       </c>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>S-04</t>
+          <t>V-09</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>販売制限を解除する基準</t>
+          <t>価格変更の頻度上限</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E58" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>1日1回,1日2回,制限なし</t>
+        </is>
+      </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>7日前・残≥20%</t>
+          <t>1日1回（直前7日は2回）</t>
         </is>
       </c>
       <c r="G58" s="6" t="n"/>
       <c r="H58" s="6" t="n"/>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
-          <t>G-11</t>
+          <t>E-31</t>
         </is>
       </c>
       <c r="K58" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-DP-01</t>
         </is>
       </c>
     </row>
     <row r="59" ht="32" customHeight="1">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>S-05</t>
+          <t>V-10</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>オーバーブッキングを実施しているか</t>
+          <t>繁忙日に段階的値上げを始める稼働率の節目</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E59" s="11" t="inlineStr">
-        <is>
-          <t>実施している,実施していない</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr"/>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>実施していない</t>
+          <t>50 / 70 / 85%</t>
         </is>
       </c>
       <c r="G59" s="6" t="n"/>
       <c r="H59" s="6" t="n"/>
-      <c r="I59" s="12" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="J59" s="11" t="inlineStr">
         <is>
-          <t>G-07</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="K59" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-DP-01</t>
         </is>
       </c>
     </row>
     <row r="60" ht="32" customHeight="1">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>S-06</t>
+          <t>V-11</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>実績のノーショー率（概算）</t>
+          <t>残室が僅少（5%以下）のとき価格を上限で維持するか</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E60" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>維持する,通常どおり</t>
+        </is>
+      </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>1%未満</t>
+          <t>維持する</t>
         </is>
       </c>
       <c r="G60" s="6" t="n"/>
@@ -3493,74 +3505,78 @@
       </c>
       <c r="J60" s="11" t="inlineStr">
         <is>
-          <t>G-07</t>
+          <t>E-17</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-DP-01</t>
         </is>
       </c>
     </row>
     <row r="61" ht="32" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>S-07</t>
+          <t>V-12</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>団体ブロックの解放期限（団体種別ごとに）</t>
+          <t>直前（3日前以内）の値下げを認めるか</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E61" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>条件付きで認める,認めない,制限なし</t>
+        </is>
+      </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>繁忙60日前 / 閑散14日前</t>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="G61" s="6" t="n"/>
       <c r="H61" s="6" t="n"/>
-      <c r="I61" s="11" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="I61" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="J61" s="11" t="inlineStr">
         <is>
-          <t>G-09</t>
+          <t>E-19 / R-02</t>
         </is>
       </c>
       <c r="K61" s="11" t="inlineStr">
         <is>
-          <t>GroupBooking</t>
+          <t>Alert</t>
         </is>
       </c>
     </row>
     <row r="62" ht="32" customHeight="1">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>S-08</t>
+          <t>V-13</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>直販用の在庫確保をしているか</t>
+          <t>価格の下限を原価から算出しているか</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
@@ -3570,7 +3586,7 @@
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>サイトコントローラーで制御,していない,その他</t>
+          <t>算出している,していない</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
@@ -3582,12 +3598,12 @@
       <c r="H62" s="6" t="n"/>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="J62" s="11" t="inlineStr">
         <is>
-          <t>G-10</t>
+          <t>E-34</t>
         </is>
       </c>
       <c r="K62" s="11" t="inlineStr">
@@ -3599,62 +3615,66 @@
     <row r="63" ht="32" customHeight="1">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>S-09</t>
+          <t>V-14</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>キャンセルポリシー（無料期限・料率）</t>
+          <t>返金不可プラン・早割プランの有無</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E63" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>両方あり,早割のみ,返金不可のみ,なし</t>
+        </is>
+      </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="G63" s="6" t="n"/>
       <c r="H63" s="6" t="n"/>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="J63" s="11" t="inlineStr">
         <is>
-          <t>G-14</t>
+          <t>E-26</t>
         </is>
       </c>
       <c r="K63" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Campaign</t>
         </is>
       </c>
     </row>
     <row r="64" ht="32" customHeight="1">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>S-10</t>
+          <t>V-15</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>利用中のサイトコントローラー名</t>
+          <t>需要レベル（A〜E）を判定する稼働率の目安</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
@@ -3665,152 +3685,152 @@
       <c r="E64" s="11" t="inlineStr"/>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A:85%以上 B:70% C:50% D:30% E:30%未満</t>
         </is>
       </c>
       <c r="G64" s="6" t="n"/>
       <c r="H64" s="6" t="n"/>
-      <c r="I64" s="12" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="J64" s="11" t="inlineStr">
         <is>
-          <t>B-10</t>
+          <t>§3.1</t>
         </is>
       </c>
       <c r="K64" s="11" t="inlineStr">
         <is>
+          <t>DemandLevel</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>V-16</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>価格運用</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>リードタイムの区切り（何日前を境に運用を変えるか）</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr"/>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>60日 / 30日 / 14日 / 7日 / 3日</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="n"/>
+      <c r="H65" s="6" t="n"/>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J65" s="11" t="inlineStr">
+        <is>
+          <t>§3.2</t>
+        </is>
+      </c>
+      <c r="K65" s="11" t="inlineStr">
+        <is>
           <t>F-DP-01</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>■ データ連携</t>
-        </is>
-      </c>
-      <c r="B65" s="9" t="n"/>
-      <c r="C65" s="9" t="n"/>
-      <c r="D65" s="9" t="n"/>
-      <c r="E65" s="9" t="n"/>
-      <c r="F65" s="9" t="n"/>
-      <c r="G65" s="9" t="n"/>
-      <c r="H65" s="9" t="n"/>
-      <c r="I65" s="9" t="n"/>
-      <c r="J65" s="9" t="n"/>
-      <c r="K65" s="9" t="n"/>
-    </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>D-01</t>
-        </is>
-      </c>
-      <c r="B66" s="11" t="inlineStr">
-        <is>
-          <t>データ連携</t>
-        </is>
-      </c>
-      <c r="C66" s="11" t="inlineStr">
-        <is>
-          <t>【最重要】PMSから販売室数（部屋数）を出力できるか</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E66" s="11" t="inlineStr">
-        <is>
-          <t>出せる,出せない,確認中</t>
-        </is>
-      </c>
-      <c r="F66" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="n"/>
-      <c r="H66" s="6" t="n"/>
-      <c r="I66" s="12" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="J66" s="11" t="inlineStr">
-        <is>
-          <t>§1.4</t>
-        </is>
-      </c>
-      <c r="K66" s="11" t="inlineStr">
-        <is>
-          <t>DailyData.soldRooms</t>
-        </is>
-      </c>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>■ 在庫・販売制限</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="n"/>
+      <c r="C66" s="9" t="n"/>
+      <c r="D66" s="9" t="n"/>
+      <c r="E66" s="9" t="n"/>
+      <c r="F66" s="9" t="n"/>
+      <c r="G66" s="9" t="n"/>
+      <c r="H66" s="9" t="n"/>
+      <c r="I66" s="9" t="n"/>
+      <c r="J66" s="9" t="n"/>
+      <c r="K66" s="9" t="n"/>
     </row>
     <row r="67" ht="32" customHeight="1">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>S-01</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>PMSの製品名</t>
+          <t>CTA（到着日クローズ）を使うか</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E67" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>使う,使わない</t>
+        </is>
+      </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>使わない</t>
         </is>
       </c>
       <c r="G67" s="6" t="n"/>
       <c r="H67" s="6" t="n"/>
-      <c r="I67" s="12" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="J67" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="K67" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>推奨提示のみ</t>
         </is>
       </c>
     </row>
     <row r="68" ht="32" customHeight="1">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>S-02</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>予約データの出力形式</t>
+          <t>CTD（出発日クローズ）を使うか</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
@@ -3820,46 +3840,46 @@
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>xlsx,CSV,TSV,その他</t>
+          <t>使う,使わない</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>CSV</t>
+          <t>使わない</t>
         </is>
       </c>
       <c r="G68" s="6" t="n"/>
       <c r="H68" s="6" t="n"/>
-      <c r="I68" s="12" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="J68" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="K68" s="11" t="inlineStr">
         <is>
-          <t>取込</t>
+          <t>推奨提示のみ</t>
         </is>
       </c>
     </row>
     <row r="69" ht="32" customHeight="1">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>S-03</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>出力の頻度</t>
+          <t>繁忙時に高手数料チャネルを売り止めるか</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
@@ -3869,46 +3889,46 @@
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>毎日,週次,都度手動</t>
+          <t>売り止める,売り止めない</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>毎日</t>
+          <t>売り止める</t>
         </is>
       </c>
       <c r="G69" s="6" t="n"/>
       <c r="H69" s="6" t="n"/>
-      <c r="I69" s="12" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="J69" s="11" t="inlineStr">
         <is>
-          <t>B-07</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="K69" s="11" t="inlineStr">
         <is>
-          <t>BookingCurveData</t>
+          <t>OtaChannelData</t>
         </is>
       </c>
     </row>
     <row r="70" ht="32" customHeight="1">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>D-05</t>
+          <t>S-04</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>1日のうち何回・何時に出力できるか</t>
+          <t>販売制限を解除する基準</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
@@ -3919,41 +3939,41 @@
       <c r="E70" s="11" t="inlineStr"/>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>日次固定時刻（直前7日は朝夕2回）</t>
+          <t>7日前・残≥20%</t>
         </is>
       </c>
       <c r="G70" s="6" t="n"/>
       <c r="H70" s="6" t="n"/>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="J70" s="11" t="inlineStr">
         <is>
-          <t>B-07</t>
+          <t>G-11</t>
         </is>
       </c>
       <c r="K70" s="11" t="inlineStr">
         <is>
-          <t>AG-10</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="71" ht="32" customHeight="1">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>D-06</t>
+          <t>S-05</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>自動出力の可否</t>
+          <t>オーバーブッキングを実施しているか</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
@@ -3963,12 +3983,12 @@
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>定時フォルダ配置,FTP,メール添付,手動のみ</t>
+          <t>実施している,実施していない</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>手動のみ</t>
+          <t>実施していない</t>
         </is>
       </c>
       <c r="G71" s="6" t="n"/>
@@ -3980,44 +4000,40 @@
       </c>
       <c r="J71" s="11" t="inlineStr">
         <is>
+          <t>G-07</t>
+        </is>
+      </c>
+      <c r="K71" s="11" t="inlineStr">
+        <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="11" t="inlineStr">
-        <is>
-          <t>取込</t>
         </is>
       </c>
     </row>
     <row r="72" ht="32" customHeight="1">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>D-07</t>
+          <t>S-06</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>差分抽出（予約変更日以降など）ができるか</t>
+          <t>実績のノーショー率（概算）</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E72" s="11" t="inlineStr">
-        <is>
-          <t>できる,できない</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr"/>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>できない</t>
+          <t>1%未満</t>
         </is>
       </c>
       <c r="G72" s="6" t="n"/>
@@ -4029,29 +4045,29 @@
       </c>
       <c r="J72" s="11" t="inlineStr">
         <is>
+          <t>G-07</t>
+        </is>
+      </c>
+      <c r="K72" s="11" t="inlineStr">
+        <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="11" t="inlineStr">
-        <is>
-          <t>ImportBatch</t>
         </is>
       </c>
     </row>
     <row r="73" ht="32" customHeight="1">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>D-08</t>
+          <t>S-07</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>過去実績を何年分まで遡って出力できるか</t>
+          <t>団体ブロックの解放期限（団体種別ごとに）</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
@@ -4062,41 +4078,41 @@
       <c r="E73" s="11" t="inlineStr"/>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>繁忙60日前 / 閑散14日前</t>
         </is>
       </c>
       <c r="G73" s="6" t="n"/>
       <c r="H73" s="6" t="n"/>
-      <c r="I73" s="12" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="J73" s="11" t="inlineStr">
         <is>
-          <t>B-12</t>
+          <t>G-09</t>
         </is>
       </c>
       <c r="K73" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>GroupBooking</t>
         </is>
       </c>
     </row>
     <row r="74" ht="32" customHeight="1">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>D-09</t>
+          <t>S-08</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>取消（CXL）レコードは出力に残り続けるか</t>
+          <t>直販用の在庫確保をしているか</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
@@ -4106,58 +4122,54 @@
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>残る,消える,不明</t>
+          <t>サイトコントローラーで制御,していない,その他</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>残る</t>
+          <t>していない</t>
         </is>
       </c>
       <c r="G74" s="6" t="n"/>
       <c r="H74" s="6" t="n"/>
-      <c r="I74" s="12" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="J74" s="11" t="inlineStr">
         <is>
-          <t>§1.5</t>
+          <t>G-10</t>
         </is>
       </c>
       <c r="K74" s="11" t="inlineStr">
         <is>
-          <t>Reservation</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="75" ht="32" customHeight="1">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>S-09</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>予約明細を一意にするキー（レコードID）を出力できるか</t>
+          <t>キャンセルポリシー（無料期限・料率）</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="inlineStr">
-        <is>
-          <t>できる,できない</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr"/>
       <c r="F75" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -4165,51 +4177,47 @@
       </c>
       <c r="G75" s="6" t="n"/>
       <c r="H75" s="6" t="n"/>
-      <c r="I75" s="12" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="J75" s="11" t="inlineStr">
         <is>
-          <t>§1.5</t>
+          <t>G-14</t>
         </is>
       </c>
       <c r="K75" s="11" t="inlineStr">
         <is>
-          <t>Reservation.sourceRowNo</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="76" ht="32" customHeight="1">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>S-10</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>日別の宿泊人数が取得できるか（泊ごとに人数が変わる予約）</t>
+          <t>利用中のサイトコントローラー名</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E76" s="11" t="inlineStr">
-        <is>
-          <t>取得できる,できない</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr"/>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>できない</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G76" s="6" t="n"/>
@@ -4221,68 +4229,36 @@
       </c>
       <c r="J76" s="11" t="inlineStr">
         <is>
-          <t>§1.3</t>
+          <t>B-10</t>
         </is>
       </c>
       <c r="K76" s="11" t="inlineStr">
         <is>
-          <t>ReservationNight</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="32" customHeight="1">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>D-12</t>
-        </is>
-      </c>
-      <c r="B77" s="11" t="inlineStr">
-        <is>
-          <t>データ連携</t>
-        </is>
-      </c>
-      <c r="C77" s="11" t="inlineStr">
-        <is>
-          <t>デイユース（泊数0）のレコードが存在するか</t>
-        </is>
-      </c>
-      <c r="D77" s="11" t="inlineStr">
-        <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E77" s="11" t="inlineStr">
-        <is>
-          <t>ある,ない</t>
-        </is>
-      </c>
-      <c r="F77" s="11" t="inlineStr">
-        <is>
-          <t>ない</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="n"/>
-      <c r="H77" s="6" t="n"/>
-      <c r="I77" s="11" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="J77" s="11" t="inlineStr">
-        <is>
-          <t>§1.5</t>
-        </is>
-      </c>
-      <c r="K77" s="11" t="inlineStr">
-        <is>
-          <t>取込</t>
-        </is>
-      </c>
+          <t>F-DP-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>■ データ連携</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="n"/>
+      <c r="C77" s="9" t="n"/>
+      <c r="D77" s="9" t="n"/>
+      <c r="E77" s="9" t="n"/>
+      <c r="F77" s="9" t="n"/>
+      <c r="G77" s="9" t="n"/>
+      <c r="H77" s="9" t="n"/>
+      <c r="I77" s="9" t="n"/>
+      <c r="J77" s="9" t="n"/>
+      <c r="K77" s="9" t="n"/>
     </row>
     <row r="78" ht="32" customHeight="1">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
@@ -4292,7 +4268,7 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>部屋タイプコードの対応表を提供できるか</t>
+          <t>【最重要】PMSから販売室数（部屋数）を出力できるか</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
@@ -4302,7 +4278,7 @@
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>できる,できない</t>
+          <t>出せる,出せない,確認中</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
@@ -4319,19 +4295,19 @@
       </c>
       <c r="J78" s="11" t="inlineStr">
         <is>
-          <t>§1.5</t>
+          <t>§1.4</t>
         </is>
       </c>
       <c r="K78" s="11" t="inlineStr">
         <is>
-          <t>RoomType</t>
+          <t>DailyData.soldRooms</t>
         </is>
       </c>
     </row>
     <row r="79" ht="32" customHeight="1">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
@@ -4341,19 +4317,15 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Market / エージェント / 地域コードの対応表を提供できるか</t>
+          <t>PMSの製品名</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E79" s="11" t="inlineStr">
-        <is>
-          <t>できる,できない</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr"/>
       <c r="F79" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -4361,9 +4333,9 @@
       </c>
       <c r="G79" s="6" t="n"/>
       <c r="H79" s="6" t="n"/>
-      <c r="I79" s="11" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="I79" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr">
@@ -4380,7 +4352,7 @@
     <row r="80" ht="32" customHeight="1">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
@@ -4390,7 +4362,7 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>個人情報（氏名・会社名・電話番号）を連携対象に含めるか</t>
+          <t>予約データの出力形式</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
@@ -4400,12 +4372,12 @@
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>含めない,含める</t>
+          <t>xlsx,CSV,TSV,その他</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>含めない</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="G80" s="6" t="n"/>
@@ -4417,7 +4389,7 @@
       </c>
       <c r="J80" s="11" t="inlineStr">
         <is>
-          <t>AG-12</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K80" s="11" t="inlineStr">
@@ -4426,37 +4398,69 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>■ セグメント・団体</t>
-        </is>
-      </c>
-      <c r="B81" s="9" t="n"/>
-      <c r="C81" s="9" t="n"/>
-      <c r="D81" s="9" t="n"/>
-      <c r="E81" s="9" t="n"/>
-      <c r="F81" s="9" t="n"/>
-      <c r="G81" s="9" t="n"/>
-      <c r="H81" s="9" t="n"/>
-      <c r="I81" s="9" t="n"/>
-      <c r="J81" s="9" t="n"/>
-      <c r="K81" s="9" t="n"/>
+    <row r="81" ht="32" customHeight="1">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>D-04</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>データ連携</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>出力の頻度</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>毎日,週次,都度手動</t>
+        </is>
+      </c>
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>毎日</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="n"/>
+      <c r="H81" s="6" t="n"/>
+      <c r="I81" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J81" s="11" t="inlineStr">
+        <is>
+          <t>B-07</t>
+        </is>
+      </c>
+      <c r="K81" s="11" t="inlineStr">
+        <is>
+          <t>BookingCurveData</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="32" customHeight="1">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>D-05</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>セグメント・団体</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>セグメント区分（PMSのマスタ）を列挙</t>
+          <t>1日のうち何回・何時に出力できるか</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
@@ -4467,41 +4471,41 @@
       <c r="E82" s="11" t="inlineStr"/>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>日次固定時刻（直前7日は朝夕2回）</t>
         </is>
       </c>
       <c r="G82" s="6" t="n"/>
       <c r="H82" s="6" t="n"/>
-      <c r="I82" s="12" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr">
         <is>
-          <t>K-01</t>
+          <t>B-07</t>
         </is>
       </c>
       <c r="K82" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AG-10</t>
         </is>
       </c>
     </row>
     <row r="83" ht="32" customHeight="1">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>D-06</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>セグメント・団体</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>団体に「確度」を設定しているか</t>
+          <t>自動出力の可否</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
@@ -4511,12 +4515,12 @@
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>設定している,していない</t>
+          <t>定時フォルダ配置,FTP,メール添付,手動のみ</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>していない</t>
+          <t>手動のみ</t>
         </is>
       </c>
       <c r="G83" s="6" t="n"/>
@@ -4528,40 +4532,44 @@
       </c>
       <c r="J83" s="11" t="inlineStr">
         <is>
-          <t>B-06 / AG-06</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K83" s="11" t="inlineStr">
         <is>
-          <t>GroupBooking.status</t>
+          <t>取込</t>
         </is>
       </c>
     </row>
     <row r="84" ht="32" customHeight="1">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>D-07</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>セグメント・団体</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>（設定している場合）確度の区分</t>
+          <t>差分抽出（予約変更日以降など）ができるか</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E84" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>できる,できない</t>
+        </is>
+      </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>ブロック / A / B / C</t>
+          <t>できない</t>
         </is>
       </c>
       <c r="G84" s="6" t="n"/>
@@ -4573,41 +4581,37 @@
       </c>
       <c r="J84" s="11" t="inlineStr">
         <is>
-          <t>B-06</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K84" s="11" t="inlineStr">
         <is>
-          <t>GroupBooking</t>
+          <t>ImportBatch</t>
         </is>
       </c>
     </row>
     <row r="85" ht="32" customHeight="1">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>D-08</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>セグメント・団体</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>団体ブロックのPMS上の持ち方</t>
+          <t>過去実績を何年分まで遡って出力できるか</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E85" s="11" t="inlineStr">
-        <is>
-          <t>ブロック枠,実予約,仮予約,混在</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr"/>
       <c r="F85" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -4622,74 +4626,78 @@
       </c>
       <c r="J85" s="11" t="inlineStr">
         <is>
-          <t>A-19</t>
+          <t>B-12</t>
         </is>
       </c>
       <c r="K85" s="11" t="inlineStr">
         <is>
-          <t>取込</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="86" ht="32" customHeight="1">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>G-05</t>
+          <t>D-09</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>セグメント・団体</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>ウォッシュ率（団体の実際の戻り率）の実績値</t>
+          <t>取消（CXL）レコードは出力に残り続けるか</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E86" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>残る,消える,不明</t>
+        </is>
+      </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>残る</t>
         </is>
       </c>
       <c r="G86" s="6" t="n"/>
       <c r="H86" s="6" t="n"/>
-      <c r="I86" s="11" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="I86" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="J86" s="11" t="inlineStr">
         <is>
-          <t>A-19 / K-06</t>
+          <t>§1.5</t>
         </is>
       </c>
       <c r="K86" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Reservation</t>
         </is>
       </c>
     </row>
     <row r="87" ht="32" customHeight="1">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>G-06</t>
+          <t>D-10</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>セグメント・団体</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>インバウンドの早期販売を制限しているか</t>
+          <t>予約明細を一意にするキー（レコードID）を出力できるか</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
@@ -4699,46 +4707,46 @@
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>制限している,していない</t>
+          <t>できる,できない</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>していない</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G87" s="6" t="n"/>
       <c r="H87" s="6" t="n"/>
-      <c r="I87" s="11" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="I87" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr">
         <is>
-          <t>K-12</t>
+          <t>§1.5</t>
         </is>
       </c>
       <c r="K87" s="11" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Reservation.sourceRowNo</t>
         </is>
       </c>
     </row>
     <row r="88" ht="32" customHeight="1">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>G-07</t>
+          <t>D-11</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>セグメント・団体</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>月別のセグメントミックス目標があるか</t>
+          <t>日別の宿泊人数が取得できるか（泊ごとに人数が変わる予約）</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
@@ -4748,46 +4756,46 @@
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>ある,ない</t>
+          <t>取得できる,できない</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>ない</t>
+          <t>できない</t>
         </is>
       </c>
       <c r="G88" s="6" t="n"/>
       <c r="H88" s="6" t="n"/>
-      <c r="I88" s="11" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="I88" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="J88" s="11" t="inlineStr">
         <is>
-          <t>K-13</t>
+          <t>§1.3</t>
         </is>
       </c>
       <c r="K88" s="11" t="inlineStr">
         <is>
-          <t>MonthlyBudget</t>
+          <t>ReservationNight</t>
         </is>
       </c>
     </row>
     <row r="89" ht="32" customHeight="1">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>G-08</t>
+          <t>D-12</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>セグメント・団体</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>団体を画面上で区別して表示する必要があるか</t>
+          <t>デイユース（泊数0）のレコードが存在するか</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
@@ -4797,71 +4805,107 @@
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>必要,不要</t>
+          <t>ある,ない</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>必要</t>
+          <t>ない</t>
         </is>
       </c>
       <c r="G89" s="6" t="n"/>
       <c r="H89" s="6" t="n"/>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>K-14</t>
+          <t>§1.5</t>
         </is>
       </c>
       <c r="K89" s="11" t="inlineStr">
         <is>
-          <t>F-DAILY-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="22" customHeight="1">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>■ 競合・チャネル</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="n"/>
-      <c r="C90" s="9" t="n"/>
-      <c r="D90" s="9" t="n"/>
-      <c r="E90" s="9" t="n"/>
-      <c r="F90" s="9" t="n"/>
-      <c r="G90" s="9" t="n"/>
-      <c r="H90" s="9" t="n"/>
-      <c r="I90" s="9" t="n"/>
-      <c r="J90" s="9" t="n"/>
-      <c r="K90" s="9" t="n"/>
+          <t>取込</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="32" customHeight="1">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>データ連携</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>部屋タイプコードの対応表を提供できるか</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>できる,できない</t>
+        </is>
+      </c>
+      <c r="F90" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="n"/>
+      <c r="H90" s="6" t="n"/>
+      <c r="I90" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J90" s="11" t="inlineStr">
+        <is>
+          <t>§1.5</t>
+        </is>
+      </c>
+      <c r="K90" s="11" t="inlineStr">
+        <is>
+          <t>RoomType</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="32" customHeight="1">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>競合・チャネル</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>競合ホテル（最大5社）</t>
+          <t>Market / エージェント / 地域コードの対応表を提供できるか</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E91" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>できる,できない</t>
+        </is>
+      </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -4869,36 +4913,36 @@
       </c>
       <c r="G91" s="6" t="n"/>
       <c r="H91" s="6" t="n"/>
-      <c r="I91" s="12" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="J91" s="11" t="inlineStr">
         <is>
-          <t>F-SET-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K91" s="11" t="inlineStr">
         <is>
-          <t>Competitor</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="92" ht="32" customHeight="1">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>D-15</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>競合・チャネル</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>競合のOTA別URL（提供可否）</t>
+          <t>個人情報（氏名・会社名・電話番号）を連携対象に含めるか</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
@@ -4908,12 +4952,12 @@
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>提供できる,提供できない</t>
+          <t>含めない,含める</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>含めない</t>
         </is>
       </c>
       <c r="G92" s="6" t="n"/>
@@ -4925,172 +4969,140 @@
       </c>
       <c r="J92" s="11" t="inlineStr">
         <is>
-          <t>F-SET-03</t>
+          <t>AG-12</t>
         </is>
       </c>
       <c r="K92" s="11" t="inlineStr">
         <is>
-          <t>Competitor</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="32" customHeight="1">
-      <c r="A93" s="10" t="inlineStr">
-        <is>
-          <t>C-03</t>
-        </is>
-      </c>
-      <c r="B93" s="11" t="inlineStr">
-        <is>
-          <t>競合・チャネル</t>
-        </is>
-      </c>
-      <c r="C93" s="11" t="inlineStr">
-        <is>
-          <t>競合比較の基準人数</t>
-        </is>
-      </c>
-      <c r="D93" s="11" t="inlineStr">
-        <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E93" s="11" t="inlineStr">
-        <is>
-          <t>1名,2名</t>
-        </is>
-      </c>
-      <c r="F93" s="11" t="inlineStr">
-        <is>
-          <t>2名</t>
-        </is>
-      </c>
-      <c r="G93" s="6" t="n"/>
-      <c r="H93" s="6" t="n"/>
-      <c r="I93" s="12" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="J93" s="11" t="inlineStr">
-        <is>
-          <t>B-08</t>
-        </is>
-      </c>
-      <c r="K93" s="11" t="inlineStr">
-        <is>
-          <t>F-DAILY-03</t>
-        </is>
-      </c>
+          <t>取込</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>■ セグメント・団体</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="n"/>
+      <c r="C93" s="9" t="n"/>
+      <c r="D93" s="9" t="n"/>
+      <c r="E93" s="9" t="n"/>
+      <c r="F93" s="9" t="n"/>
+      <c r="G93" s="9" t="n"/>
+      <c r="H93" s="9" t="n"/>
+      <c r="I93" s="9" t="n"/>
+      <c r="J93" s="9" t="n"/>
+      <c r="K93" s="9" t="n"/>
     </row>
     <row r="94" ht="32" customHeight="1">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>競合・チャネル</t>
+          <t>セグメント・団体</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>競合比較で食事条件を揃えるか</t>
+          <t>セグメント区分（PMSのマスタ）を列挙</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E94" s="11" t="inlineStr">
-        <is>
-          <t>食事なしで揃える,朝食付で揃える</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E94" s="11" t="inlineStr"/>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>食事なし</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G94" s="6" t="n"/>
       <c r="H94" s="6" t="n"/>
-      <c r="I94" s="11" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="I94" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="J94" s="11" t="inlineStr">
         <is>
-          <t>B-08</t>
+          <t>K-01</t>
         </is>
       </c>
       <c r="K94" s="11" t="inlineStr">
         <is>
-          <t>F-DAILY-03</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="95" ht="32" customHeight="1">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>C-05</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>競合・チャネル</t>
+          <t>セグメント・団体</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>レートパリティの許容幅</t>
+          <t>団体に「確度」を設定しているか</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E95" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>設定している,していない</t>
+        </is>
+      </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>±3%</t>
+          <t>していない</t>
         </is>
       </c>
       <c r="G95" s="6" t="n"/>
       <c r="H95" s="6" t="n"/>
-      <c r="I95" s="11" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="I95" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="J95" s="11" t="inlineStr">
         <is>
-          <t>I-11</t>
+          <t>B-06 / AG-06</t>
         </is>
       </c>
       <c r="K95" s="11" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>GroupBooking.status</t>
         </is>
       </c>
     </row>
     <row r="96" ht="32" customHeight="1">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>C-06</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>競合・チャネル</t>
+          <t>セグメント・団体</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>直販比率の目標値</t>
+          <t>（設定している場合）確度の区分</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
@@ -5101,7 +5113,7 @@
       <c r="E96" s="11" t="inlineStr"/>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>ブロック / A / B / C</t>
         </is>
       </c>
       <c r="G96" s="6" t="n"/>
@@ -5113,101 +5125,101 @@
       </c>
       <c r="J96" s="11" t="inlineStr">
         <is>
-          <t>J-05</t>
+          <t>B-06</t>
         </is>
       </c>
       <c r="K96" s="11" t="inlineStr">
         <is>
-          <t>OtaChannelData</t>
+          <t>GroupBooking</t>
         </is>
       </c>
     </row>
     <row r="97" ht="32" customHeight="1">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>C-07</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>競合・チャネル</t>
+          <t>セグメント・団体</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>繁忙日に絞りたいチャネル</t>
+          <t>団体ブロックのPMS上の持ち方</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E97" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>ブロック枠,実予約,仮予約,混在</t>
+        </is>
+      </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>高手数料チャネル</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G97" s="6" t="n"/>
       <c r="H97" s="6" t="n"/>
-      <c r="I97" s="11" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="I97" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="J97" s="11" t="inlineStr">
         <is>
-          <t>J-07</t>
+          <t>A-19</t>
         </is>
       </c>
       <c r="K97" s="11" t="inlineStr">
         <is>
-          <t>OtaChannelData</t>
+          <t>取込</t>
         </is>
       </c>
     </row>
     <row r="98" ht="32" customHeight="1">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>C-08</t>
+          <t>G-05</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>競合・チャネル</t>
+          <t>セグメント・団体</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>OTAとの特約（販促サポート等）の有無</t>
+          <t>ウォッシュ率（団体の実際の戻り率）の実績値</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E98" s="11" t="inlineStr">
-        <is>
-          <t>ある,ない</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr"/>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G98" s="6" t="n"/>
       <c r="H98" s="6" t="n"/>
       <c r="I98" s="11" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="J98" s="11" t="inlineStr">
         <is>
-          <t>J-07</t>
+          <t>A-19 / K-06</t>
         </is>
       </c>
       <c r="K98" s="11" t="inlineStr">
@@ -5216,82 +5228,118 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="22" customHeight="1">
-      <c r="A99" s="8" t="inlineStr">
-        <is>
-          <t>■ 運用体制</t>
-        </is>
-      </c>
-      <c r="B99" s="9" t="n"/>
-      <c r="C99" s="9" t="n"/>
-      <c r="D99" s="9" t="n"/>
-      <c r="E99" s="9" t="n"/>
-      <c r="F99" s="9" t="n"/>
-      <c r="G99" s="9" t="n"/>
-      <c r="H99" s="9" t="n"/>
-      <c r="I99" s="9" t="n"/>
-      <c r="J99" s="9" t="n"/>
-      <c r="K99" s="9" t="n"/>
+    <row r="99" ht="32" customHeight="1">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>G-06</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>セグメント・団体</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>インバウンドの早期販売を制限しているか</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>制限している,していない</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>していない</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="n"/>
+      <c r="H99" s="6" t="n"/>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J99" s="11" t="inlineStr">
+        <is>
+          <t>K-12</t>
+        </is>
+      </c>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>Campaign</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="32" customHeight="1">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>O-01</t>
+          <t>G-07</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>運用体制</t>
+          <t>セグメント・団体</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>価格変更を判断する人（役職・人数）</t>
+          <t>月別のセグメントミックス目標があるか</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E100" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>ある,ない</t>
+        </is>
+      </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ない</t>
         </is>
       </c>
       <c r="G100" s="6" t="n"/>
       <c r="H100" s="6" t="n"/>
-      <c r="I100" s="12" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="I100" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="J100" s="11" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>K-13</t>
         </is>
       </c>
       <c r="K100" s="11" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>MonthlyBudget</t>
         </is>
       </c>
     </row>
     <row r="101" ht="32" customHeight="1">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>O-02</t>
+          <t>G-08</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>運用体制</t>
+          <t>セグメント・団体</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>価格見直しの頻度</t>
+          <t>団体を画面上で区別して表示する必要があるか</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
@@ -5301,95 +5349,63 @@
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>毎日,週次,月次,不定期</t>
+          <t>必要,不要</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>毎日</t>
+          <t>必要</t>
         </is>
       </c>
       <c r="G101" s="6" t="n"/>
       <c r="H101" s="6" t="n"/>
-      <c r="I101" s="12" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="J101" s="11" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>K-14</t>
         </is>
       </c>
       <c r="K101" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="32" customHeight="1">
-      <c r="A102" s="10" t="inlineStr">
-        <is>
-          <t>O-03</t>
-        </is>
-      </c>
-      <c r="B102" s="11" t="inlineStr">
-        <is>
-          <t>運用体制</t>
-        </is>
-      </c>
-      <c r="C102" s="11" t="inlineStr">
-        <is>
-          <t>週次で人が確認しオペレーターが操作する運用でよいか</t>
-        </is>
-      </c>
-      <c r="D102" s="11" t="inlineStr">
-        <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E102" s="11" t="inlineStr">
-        <is>
-          <t>よい,別の体制がよい</t>
-        </is>
-      </c>
-      <c r="F102" s="11" t="inlineStr">
-        <is>
-          <t>よい</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="n"/>
-      <c r="H102" s="6" t="n"/>
-      <c r="I102" s="11" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="J102" s="11" t="inlineStr">
-        <is>
-          <t>M-04 / AG-09</t>
-        </is>
-      </c>
-      <c r="K102" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>F-DAILY-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>■ 競合・チャネル</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="n"/>
+      <c r="C102" s="9" t="n"/>
+      <c r="D102" s="9" t="n"/>
+      <c r="E102" s="9" t="n"/>
+      <c r="F102" s="9" t="n"/>
+      <c r="G102" s="9" t="n"/>
+      <c r="H102" s="9" t="n"/>
+      <c r="I102" s="9" t="n"/>
+      <c r="J102" s="9" t="n"/>
+      <c r="K102" s="9" t="n"/>
     </row>
     <row r="103" ht="32" customHeight="1">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>O-04</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>運用体制</t>
+          <t>競合・チャネル</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>着地が予算を超過しそうなときの打ち手</t>
+          <t>競合ホテル（最大5社）</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
@@ -5405,36 +5421,36 @@
       </c>
       <c r="G103" s="6" t="n"/>
       <c r="H103" s="6" t="n"/>
-      <c r="I103" s="11" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="I103" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="J103" s="11" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>F-SET-03</t>
         </is>
       </c>
       <c r="K103" s="11" t="inlineStr">
         <is>
-          <t>F-DP-04</t>
+          <t>Competitor</t>
         </is>
       </c>
     </row>
     <row r="104" ht="32" customHeight="1">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>O-05</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>運用体制</t>
+          <t>競合・チャネル</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>利用人数別分析の区分</t>
+          <t>競合のOTA別URL（提供可否）</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
@@ -5444,80 +5460,841 @@
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>1名/2名/3名以上,1名/2名/3名/4名以上,その他</t>
+          <t>提供できる,提供できない</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>1名/2名/3名以上</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G104" s="6" t="n"/>
       <c r="H104" s="6" t="n"/>
-      <c r="I104" s="11" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="I104" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="J104" s="11" t="inlineStr">
         <is>
-          <t>L-01 / AG-08</t>
+          <t>F-SET-03</t>
         </is>
       </c>
       <c r="K104" s="11" t="inlineStr">
         <is>
-          <t>F-ANA-01</t>
+          <t>Competitor</t>
         </is>
       </c>
     </row>
     <row r="105" ht="32" customHeight="1">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>O-06</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>運用体制</t>
+          <t>競合・チャネル</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>システム利用者のロールと人数（管理者/マネージャー/オペレーター）</t>
+          <t>競合比較の基準人数</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E105" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>1名,2名</t>
+        </is>
+      </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2名</t>
         </is>
       </c>
       <c r="G105" s="6" t="n"/>
       <c r="H105" s="6" t="n"/>
-      <c r="I105" s="11" t="inlineStr">
+      <c r="I105" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr">
+        <is>
+          <t>B-08</t>
+        </is>
+      </c>
+      <c r="K105" s="11" t="inlineStr">
+        <is>
+          <t>F-DAILY-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="32" customHeight="1">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>C-04</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>競合・チャネル</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>競合比較で食事条件を揃えるか</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>食事なしで揃える,朝食付で揃える</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>食事なし</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="n"/>
+      <c r="H106" s="6" t="n"/>
+      <c r="I106" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="J105" s="11" t="inlineStr">
+      <c r="J106" s="11" t="inlineStr">
+        <is>
+          <t>B-08</t>
+        </is>
+      </c>
+      <c r="K106" s="11" t="inlineStr">
+        <is>
+          <t>F-DAILY-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="32" customHeight="1">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>C-05</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>競合・チャネル</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>レートパリティの許容幅</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr"/>
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>±3%</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="n"/>
+      <c r="H107" s="6" t="n"/>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J107" s="11" t="inlineStr">
+        <is>
+          <t>I-11</t>
+        </is>
+      </c>
+      <c r="K107" s="11" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="32" customHeight="1">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>C-06</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>競合・チャネル</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>直販比率の目標値</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr"/>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="n"/>
+      <c r="H108" s="6" t="n"/>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J108" s="11" t="inlineStr">
+        <is>
+          <t>J-05</t>
+        </is>
+      </c>
+      <c r="K108" s="11" t="inlineStr">
+        <is>
+          <t>OtaChannelData</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="32" customHeight="1">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>C-07</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>競合・チャネル</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>繁忙日に絞りたいチャネル</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr"/>
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>高手数料チャネル</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="n"/>
+      <c r="H109" s="6" t="n"/>
+      <c r="I109" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J109" s="11" t="inlineStr">
+        <is>
+          <t>J-07</t>
+        </is>
+      </c>
+      <c r="K109" s="11" t="inlineStr">
+        <is>
+          <t>OtaChannelData</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>C-08</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t>競合・チャネル</t>
+        </is>
+      </c>
+      <c r="C110" s="11" t="inlineStr">
+        <is>
+          <t>OTAとの特約（販促サポート等）の有無</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>ある,ない</t>
+        </is>
+      </c>
+      <c r="F110" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K105" s="11" t="inlineStr">
+      <c r="G110" s="6" t="n"/>
+      <c r="H110" s="6" t="n"/>
+      <c r="I110" s="11" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J110" s="11" t="inlineStr">
+        <is>
+          <t>J-07</t>
+        </is>
+      </c>
+      <c r="K110" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="32" customHeight="1">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>C-09</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>競合・チャネル</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>現在販売されているチャネルの一覧</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="inlineStr"/>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="n"/>
+      <c r="H111" s="6" t="n"/>
+      <c r="I111" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J111" s="11" t="inlineStr">
+        <is>
+          <t>§3.2</t>
+        </is>
+      </c>
+      <c r="K111" s="11" t="inlineStr">
+        <is>
+          <t>OtaChannelData.channel</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="22" customHeight="1">
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>■ 運用体制</t>
+        </is>
+      </c>
+      <c r="B112" s="9" t="n"/>
+      <c r="C112" s="9" t="n"/>
+      <c r="D112" s="9" t="n"/>
+      <c r="E112" s="9" t="n"/>
+      <c r="F112" s="9" t="n"/>
+      <c r="G112" s="9" t="n"/>
+      <c r="H112" s="9" t="n"/>
+      <c r="I112" s="9" t="n"/>
+      <c r="J112" s="9" t="n"/>
+      <c r="K112" s="9" t="n"/>
+    </row>
+    <row r="113" ht="32" customHeight="1">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>O-01</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>運用体制</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>価格変更を判断する人（役職・人数）</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr"/>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="n"/>
+      <c r="H113" s="6" t="n"/>
+      <c r="I113" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J113" s="11" t="inlineStr">
+        <is>
+          <t>M-04</t>
+        </is>
+      </c>
+      <c r="K113" s="11" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="32" customHeight="1">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>O-02</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>運用体制</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="inlineStr">
+        <is>
+          <t>価格見直しの頻度</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>毎日,週次,月次,不定期</t>
+        </is>
+      </c>
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>毎日</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="n"/>
+      <c r="H114" s="6" t="n"/>
+      <c r="I114" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J114" s="11" t="inlineStr">
+        <is>
+          <t>M-04</t>
+        </is>
+      </c>
+      <c r="K114" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="32" customHeight="1">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>O-03</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>運用体制</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>週次で人が確認しオペレーターが操作する運用でよいか</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>よい,別の体制がよい</t>
+        </is>
+      </c>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>よい</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="n"/>
+      <c r="H115" s="6" t="n"/>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J115" s="11" t="inlineStr">
+        <is>
+          <t>M-04 / AG-09</t>
+        </is>
+      </c>
+      <c r="K115" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="32" customHeight="1">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
+          <t>O-04</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>運用体制</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>着地が予算を超過しそうなときの打ち手</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr"/>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="n"/>
+      <c r="H116" s="6" t="n"/>
+      <c r="I116" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J116" s="11" t="inlineStr">
+        <is>
+          <t>M-10</t>
+        </is>
+      </c>
+      <c r="K116" s="11" t="inlineStr">
+        <is>
+          <t>F-DP-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="32" customHeight="1">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>O-05</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>運用体制</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>利用人数別分析の区分</t>
+        </is>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>1名/2名/3名以上,1名/2名/3名/4名以上,その他</t>
+        </is>
+      </c>
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>1名/2名/3名以上</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="n"/>
+      <c r="H117" s="6" t="n"/>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J117" s="11" t="inlineStr">
+        <is>
+          <t>L-01 / AG-08</t>
+        </is>
+      </c>
+      <c r="K117" s="11" t="inlineStr">
+        <is>
+          <t>F-ANA-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="32" customHeight="1">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>O-06</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>運用体制</t>
+        </is>
+      </c>
+      <c r="C118" s="11" t="inlineStr">
+        <is>
+          <t>システム利用者のロールと人数（管理者/マネージャー/オペレーター）</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="inlineStr"/>
+      <c r="F118" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="n"/>
+      <c r="H118" s="6" t="n"/>
+      <c r="I118" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J118" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K118" s="11" t="inlineStr">
         <is>
           <t>User.role</t>
         </is>
       </c>
     </row>
+    <row r="119" ht="32" customHeight="1">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>O-07</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>運用体制</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="inlineStr">
+        <is>
+          <t>データ取込の操作を担当される方</t>
+        </is>
+      </c>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr"/>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="n"/>
+      <c r="H119" s="6" t="n"/>
+      <c r="I119" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J119" s="11" t="inlineStr">
+        <is>
+          <t>§1.6</t>
+        </is>
+      </c>
+      <c r="K119" s="11" t="inlineStr">
+        <is>
+          <t>AuditLog</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="32" customHeight="1">
+      <c r="A120" s="10" t="inlineStr">
+        <is>
+          <t>O-08</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>運用体制</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>データ取込が何日途絶えたら警告を出すか</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr"/>
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>2日</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="n"/>
+      <c r="H120" s="6" t="n"/>
+      <c r="I120" s="11" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J120" s="11" t="inlineStr">
+        <is>
+          <t>§1.6</t>
+        </is>
+      </c>
+      <c r="K120" s="11" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="32" customHeight="1">
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t>O-09</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>運用体制</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>アラートの通知先・通知方法</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr"/>
+      <c r="F121" s="11" t="inlineStr">
+        <is>
+          <t>画面表示のみ</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="n"/>
+      <c r="H121" s="6" t="n"/>
+      <c r="I121" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J121" s="11" t="inlineStr">
+        <is>
+          <t>§1.6</t>
+        </is>
+      </c>
+      <c r="K121" s="11" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="32" customHeight="1">
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>O-10</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>運用体制</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="inlineStr">
+        <is>
+          <t>イベントの影響度（大・中・小）の判断基準</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E122" s="11" t="inlineStr"/>
+      <c r="F122" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="n"/>
+      <c r="H122" s="6" t="n"/>
+      <c r="I122" s="11" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J122" s="11" t="inlineStr">
+        <is>
+          <t>§3.1</t>
+        </is>
+      </c>
+      <c r="K122" s="11" t="inlineStr">
+        <is>
+          <t>Event.expectedImpact</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K105"/>
-  <dataValidations count="48">
+  <autoFilter ref="A1:K122"/>
+  <dataValidations count="54">
     <dataValidation sqref="G5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"ビジネス,シティ,リゾート,旅館,その他"</formula1>
     </dataValidation>
@@ -5533,7 +6310,7 @@
     <dataValidation sqref="G12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"長期のみ除外,すべて除外,除外しない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G14 G15 G80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G14 G15 G92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"含めない,含める"</formula1>
     </dataValidation>
     <dataValidation sqref="G16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
@@ -5542,7 +6319,7 @@
     <dataValidation sqref="G17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"ある,ない,別システム"</formula1>
     </dataValidation>
-    <dataValidation sqref="G18 G89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G18 G101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"必要,不要"</formula1>
     </dataValidation>
     <dataValidation sqref="G19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
@@ -5557,109 +6334,127 @@
     <dataValidation sqref="G23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"売れなかった日は0として分母に含む,手動で補完する,除外する"</formula1>
     </dataValidation>
-    <dataValidation sqref="G25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+      <formula1>"料金に含む,別建て,課税なし"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G26 G27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+      <formula1>"提供できる,一部のみ,提供できない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+      <formula1>"施設全体のみ,客室タイプ別,セグメント別,併用"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+      <formula1>"持っている,持っていない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+      <formula1>"売上,稼働率,ADR,RevPAR"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"金土,土日,金土日,その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="G26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"休前日で管理したい,曜日固定でよい"</formula1>
     </dataValidation>
-    <dataValidation sqref="G32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"等比（%）,実額（円）,不定"</formula1>
     </dataValidation>
-    <dataValidation sqref="G34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"固定,月別に変える,設定なし"</formula1>
     </dataValidation>
-    <dataValidation sqref="G35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"1名基準,2名基準"</formula1>
     </dataValidation>
-    <dataValidation sqref="G37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"標準タイプからの差額,タイプ別に独立したランク"</formula1>
     </dataValidation>
-    <dataValidation sqref="G40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+      <formula1>"提供できる,提供できない,作成中"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"売上最大化,単価優先（稼働を落としても高単価）,前日より値下げしない,その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="G46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"変える,同じ"</formula1>
     </dataValidation>
-    <dataValidation sqref="G47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"1ランク,2ランク以上"</formula1>
     </dataValidation>
-    <dataValidation sqref="G48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"1日1回,1日2回,制限なし"</formula1>
     </dataValidation>
-    <dataValidation sqref="G50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"維持する,通常どおり"</formula1>
     </dataValidation>
-    <dataValidation sqref="G51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"条件付きで認める,認めない,制限なし"</formula1>
     </dataValidation>
-    <dataValidation sqref="G52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"算出している,していない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"両方あり,早割のみ,返金不可のみ,なし"</formula1>
     </dataValidation>
-    <dataValidation sqref="G55 G56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G67 G68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"使う,使わない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"売り止める,売り止めない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"実施している,実施していない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"サイトコントローラーで制御,していない,その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="G66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"出せる,出せない,確認中"</formula1>
     </dataValidation>
-    <dataValidation sqref="G68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"xlsx,CSV,TSV,その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="G69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"毎日,週次,都度手動"</formula1>
     </dataValidation>
-    <dataValidation sqref="G71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"定時フォルダ配置,FTP,メール添付,手動のみ"</formula1>
     </dataValidation>
-    <dataValidation sqref="G72 G75 G78 G79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G84 G87 G90 G91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"できる,できない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"残る,消える,不明"</formula1>
     </dataValidation>
-    <dataValidation sqref="G76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"取得できる,できない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G77 G88 G98" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G89 G100 G110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"ある,ない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"設定している,していない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"ブロック枠,実予約,仮予約,混在"</formula1>
     </dataValidation>
-    <dataValidation sqref="G87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"制限している,していない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"提供できる,提供できない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"1名,2名"</formula1>
     </dataValidation>
-    <dataValidation sqref="G94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"食事なしで揃える,朝食付で揃える"</formula1>
     </dataValidation>
-    <dataValidation sqref="G101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"毎日,週次,月次,不定期"</formula1>
     </dataValidation>
-    <dataValidation sqref="G102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"よい,別の体制がよい"</formula1>
     </dataValidation>
-    <dataValidation sqref="G104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
+    <dataValidation sqref="G117" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="選択肢外の入力" error="一覧にない値です。補足欄に詳細をご記入ください。" type="list" errorStyle="warning">
       <formula1>"1名/2名/3名以上,1名/2名/3名/4名以上,その他"</formula1>
     </dataValidation>
   </dataValidations>
